--- a/kobo/apps/kobo_cases/examples/case_management_example_form.xlsx
+++ b/kobo/apps/kobo_cases/examples/case_management_example_form.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,6 +451,11 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>parameters</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>appearance</t>
         </is>
       </c>
@@ -458,17 +463,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one mode_list</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>case_id</t>
+          <t>mode</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Case ID</t>
+          <t>Is this an existing case?</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -479,48 +484,79 @@
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>select_one_from_file cases.csv</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>known_name</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>pulldata('cases', 'name', 'case_id', ${case_id})</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+          <t>case_pick</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Select the case</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>${mode} = 'existing'</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>value=case_id,label=name</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>known_status</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>pulldata('cases', 'status', 'case_id', ${case_id})</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>case_id_new</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>New case ID</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>${mode} = 'new'</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -530,18 +566,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>known_last_visit</t>
+          <t>case_id</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>pulldata('cases', 'last_visit', 'case_id', ${case_id})</t>
+          <t>if(${mode} = 'existing', ${case_pick}, ${case_id_new})</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -551,146 +588,148 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>case_found</t>
+          <t>known_name</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>if(string-length(${known_name}) &gt; 0 or string-length(${known_status}) &gt; 0 or string-length(${known_last_visit}) &gt; 0, 'yes', 'no')</t>
+          <t>pulldata('cases', 'name', 'case_id', ${case_id})</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>known_status</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>pulldata('cases', 'status', 'case_id', ${case_id})</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>known_last_visit</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>pulldata('cases', 'last_visit', 'case_id', ${case_id})</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>existing_case</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>**Case on file**
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>**Case on file — ${case_id}**
 - Name: ${known_name}
 - Status: ${known_status}
 - Last visit: ${known_last_visit}</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>${case_found} = 'yes'</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>new_case</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>No case found for **${case_id}**. Fill in the details below and it will be created automatically when you submit.</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>${case_found} = 'no'</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>${case_found} = 'no'</t>
+          <t>${mode} = 'existing'</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one status_list</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>new_case</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>**${case_id_new}** is not in the case table yet — it will be created when you submit.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>${mode} = 'new'</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>visit_date</t>
+          <t>name_new</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Visit date</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>${mode} = 'new'</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -700,18 +739,123 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>name_fix</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Notes (not written back)</t>
+          <t>Correct the name (optional)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>${mode} = 'existing'</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>if(${mode} = 'new', ${name_new}, ${name_fix})</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>${mode} = 'new' or string-length(${name_fix}) &gt; 0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>select_one status_list</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>visit_date</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Visit date</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Notes (not written back)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -724,7 +868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -747,34 +891,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>status_list</t>
+          <t>mode_list</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>existing</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Existing case</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>status_list</t>
+          <t>mode_list</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>New case</t>
         </is>
       </c>
     </row>
@@ -786,10 +930,44 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>status_list</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>in_progress</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status_list</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>

--- a/kobo/apps/kobo_cases/examples/case_management_example_form.xlsx
+++ b/kobo/apps/kobo_cases/examples/case_management_example_form.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,25 +436,35 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>hint</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>calculation</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>relevant</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>parameters</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>appearance</t>
         </is>
@@ -463,100 +473,82 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>select_one mode_list</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>case_id</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Is this an existing case?</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>Case ID</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Type an id that exists (CASE001) or a brand new one (CASE900).</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>minimal</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>select_one_from_file cases.csv</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>case_pick</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Select the case</t>
-        </is>
-      </c>
+          <t>known_name</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>${mode} = 'existing'</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>value=case_id,label=name</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
+          <t>pulldata('cases', 'name', 'case_id', ${case_id})</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>case_id_new</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>New case ID</t>
-        </is>
-      </c>
+          <t>known_status</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>${mode} = 'new'</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>pulldata('cases', 'status', 'case_id', ${case_id})</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -566,19 +558,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>case_id</t>
+          <t>known_last_visit</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>if(${mode} = 'existing', ${case_pick}, ${case_id_new})</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>pulldata('cases', 'last_visit', 'case_id', ${case_id})</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -588,148 +582,194 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>known_name</t>
+          <t>case_found</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>pulldata('cases', 'name', 'case_id', ${case_id})</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>if(string-length(${known_name}) &gt; 0 or string-length(${known_status}) &gt; 0 or string-length(${known_last_visit}) &gt; 0, 'yes', 'no')</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>known_status</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>pulldata('cases', 'status', 'case_id', ${case_id})</t>
-        </is>
-      </c>
+          <t>existing_case</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>**Existing case — ${case_id}**
+- Name on file: ${known_name}
+- Status on file: ${known_status}
+- Last visit on file: ${known_last_visit}
+The fields below are pre-filled; change what you need.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>${case_found} = 'yes'</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>known_last_visit</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>pulldata('cases', 'last_visit', 'case_id', ${case_id})</t>
-        </is>
-      </c>
+          <t>new_case</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>**NEW — ${case_id} is not in the case table**
+It will be created when you submit. Fill in the name below.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>${case_found} = 'no'</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>existing_case</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>**Case on file — ${case_id}**
-- Name: ${known_name}
-- Status: ${known_status}
-- Last visit: ${known_last_visit}</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Pre-filled from the case table for a known case; type it in for a new one.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>${mode} = 'existing'</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>pulldata('cases', 'name', 'case_id', ${case_id})</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>${case_id}</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one status_list</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>new_case</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>**${case_id_new}** is not in the case table yet — it will be created when you submit.</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Pre-filled with the status on file.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>${mode} = 'new'</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>pulldata('cases', 'status', 'case_id', ${case_id})</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>${case_id}</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>name_new</t>
+          <t>visit_date</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Visit date</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>${mode} = 'new'</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -739,123 +779,79 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>name_fix</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Correct the name (optional)</t>
+          <t>Notes (not written back)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>${mode} = 'existing'</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>if(${mode} = 'new', ${name_new}, ${name_fix})</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>${mode} = 'new' or string-length(${name_fix}) &gt; 0</t>
-        </is>
-      </c>
+          <t>browser_intro</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>---
+**Bonus: the same case table as a dropdown**
+The list below is built live from `cases.csv` — the same file `pulldata()` reads above. It is here only to demonstrate `select_one_from_file`; it is not written back.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one status_list</t>
+          <t>select_one_from_file cases.csv</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>case_browser</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Browse existing cases (demo only)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>visit_date</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Visit date</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Notes (not written back)</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>value=case_id,label=name</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -868,7 +864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -891,34 +887,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>mode_list</t>
+          <t>status_list</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>existing</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Existing case</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mode_list</t>
+          <t>status_list</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New case</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -930,44 +926,10 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>status_list</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status_list</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
